--- a/output/pdf_financials_xlsx/GRF.xlsx
+++ b/output/pdf_financials_xlsx/GRF.xlsx
@@ -3689,10 +3689,10 @@
         <v>1.821</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>1.854</v>
+        <v>1.896</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>2.123</v>
+        <v>2.165</v>
       </c>
     </row>
     <row r="93">
@@ -9224,7 +9224,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GRF.xlsx
+++ b/output/pdf_financials_xlsx/GRF.xlsx
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.625203</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.762</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.919</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.057</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.057</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0</v>
@@ -1734,19 +1734,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.625203</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.762</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.919</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.057</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.057</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0</v>
@@ -2142,19 +2142,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.625203</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.7606309999999999</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.021</v>
+        <v>0.102</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.825</v>
+        <v>0.768</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.962</v>
+        <v>0.905</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>2.051</v>
@@ -4739,7 +4739,7 @@
         <v>-0.416</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>-0.898</v>
+        <v>-0.9</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>0</v>
@@ -4773,7 +4773,7 @@
         <v>17.084</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>-0.898</v>
+        <v>-0.9</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>0</v>
@@ -12672,7 +12672,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -18276,7 +18276,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E221" s="5" t="n">
@@ -25879,7 +25879,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -27231,7 +27235,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -31057,7 +31061,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">

--- a/output/pdf_financials_xlsx/GRF.xlsx
+++ b/output/pdf_financials_xlsx/GRF.xlsx
@@ -1028,7 +1028,7 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.171</v>
+        <v>-0.171</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0.774</v>
@@ -2918,25 +2918,25 @@
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.208</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="71">
@@ -2952,25 +2952,25 @@
         <v>0.889</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.92</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>1.253</v>
+        <v>1.334</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>1.253</v>
+        <v>1.334</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2.019</v>
+        <v>2.227</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>2.252</v>
+        <v>2.333</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>38.223</v>
+        <v>38.283</v>
       </c>
     </row>
     <row r="72">
@@ -3088,25 +3088,25 @@
         <v>3.405687</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>18.044</v>
+        <v>17.836</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>47.122</v>
+        <v>46.989</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>1.763</v>
+        <v>1.682</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="76">
@@ -3262,25 +3262,25 @@
         <v>4.674418604651163</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>1.846048580225795</v>
+        <v>1.847645113467898</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2.539989939637827</v>
+        <v>2.550176056338028</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2.539989939637827</v>
+        <v>2.550176056338028</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>9.577270859021784</v>
+        <v>9.620016440608303</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>27.07293666026871</v>
+        <v>27.15802943058221</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>18.39191643960036</v>
+        <v>18.42870118074478</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>20.69463995668652</v>
+        <v>20.72712506767731</v>
       </c>
     </row>
     <row r="81">
@@ -5183,7 +5183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M442"/>
+  <dimension ref="A1:M445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5957,7 +5957,11 @@
           <t>Current portion of lease obligation (note 6)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -14188,7 +14192,11 @@
           <t>Current portion of lease obligation (note 7)</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -15365,7 +15373,11 @@
           <t>Current portion of lease obligation (note 7) 208</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -17157,7 +17169,11 @@
           <t>Current portion of lease obligation (note 7)</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -22006,7 +22022,11 @@
           <t>Private placement (note 11)</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -22067,7 +22087,11 @@
           <t>Fees paid on private placement (note 11)</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -25208,7 +25232,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -26866,24 +26894,26 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>ended           ended</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>ended           ended</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr"/>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E364" s="5" t="n">
+        <v>-0.170713</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -26905,14 +26935,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J364" s="5" t="n">
-        <v>2.022</v>
-      </c>
-      <c r="K364" s="5" t="n">
-        <v>2.023</v>
-      </c>
-      <c r="L364" s="5" t="n">
-        <v>0.031</v>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M364" t="inlineStr">
         <is>
@@ -26923,28 +26959,22 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>ended           ended</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Revenue (note 14) $</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Increase in cash during the period</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" s="5" t="n">
+        <v>0.625203</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -26956,22 +26986,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H365" s="5" t="n">
-        <v>15.413</v>
-      </c>
-      <c r="I365" s="5" t="n">
-        <v>17.711</v>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K365" s="5" t="n">
-        <v>26.47</v>
-      </c>
-      <c r="L365" s="5" t="n">
-        <v>30.273</v>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M365" t="inlineStr">
         <is>
@@ -26982,28 +27020,26 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>ended           ended</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Cost of sales (note 15)</t>
+          <t>Cash - End of period</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E366" s="5" t="n">
+        <v>0.625203</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -27015,22 +27051,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H366" s="5" t="n">
-        <v>10.744</v>
-      </c>
-      <c r="I366" s="5" t="n">
-        <v>17.477</v>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K366" s="5" t="n">
-        <v>24.211</v>
-      </c>
-      <c r="L366" s="5" t="n">
-        <v>25.132</v>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M366" t="inlineStr">
         <is>
@@ -27051,14 +27095,10 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
+          <t>ended           ended</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -27074,20 +27114,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H367" s="5" t="n">
-        <v>4.669</v>
-      </c>
-      <c r="I367" s="5" t="n">
-        <v>0.234</v>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J367" s="5" t="n">
-        <v>0.658</v>
+        <v>2.022</v>
       </c>
       <c r="K367" s="5" t="n">
-        <v>2.259</v>
+        <v>2.023</v>
       </c>
       <c r="L367" s="5" t="n">
-        <v>5.141</v>
+        <v>0.031</v>
       </c>
       <c r="M367" t="inlineStr">
         <is>
@@ -27108,12 +27152,12 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses (note 15)</t>
+          <t>Revenue (note 14) $</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -27132,10 +27176,10 @@
         </is>
       </c>
       <c r="H368" s="5" t="n">
-        <v>2.067</v>
+        <v>15.413</v>
       </c>
       <c r="I368" s="5" t="n">
-        <v>3.299</v>
+        <v>17.711</v>
       </c>
       <c r="J368" t="inlineStr">
         <is>
@@ -27143,10 +27187,10 @@
         </is>
       </c>
       <c r="K368" s="5" t="n">
-        <v>2.918</v>
+        <v>26.47</v>
       </c>
       <c r="L368" s="5" t="n">
-        <v>3.134</v>
+        <v>30.273</v>
       </c>
       <c r="M368" t="inlineStr">
         <is>
@@ -27167,12 +27211,12 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Income (loss) from operations</t>
+          <t>Cost of sales (note 15)</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -27190,15 +27234,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H369" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I369" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H369" s="5" t="n">
+        <v>10.744</v>
+      </c>
+      <c r="I369" s="5" t="n">
+        <v>17.477</v>
       </c>
       <c r="J369" t="inlineStr">
         <is>
@@ -27206,10 +27246,10 @@
         </is>
       </c>
       <c r="K369" s="5" t="n">
-        <v>-0.659</v>
+        <v>24.211</v>
       </c>
       <c r="L369" s="5" t="n">
-        <v>2.007</v>
+        <v>25.132</v>
       </c>
       <c r="M369" t="inlineStr">
         <is>
@@ -27230,12 +27270,12 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Interest expense</t>
+          <t>Gross profit</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>GrossProfit</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -27254,19 +27294,19 @@
         </is>
       </c>
       <c r="H370" s="5" t="n">
-        <v>-0.898</v>
+        <v>4.669</v>
       </c>
       <c r="I370" s="5" t="n">
-        <v>-1.16</v>
+        <v>0.234</v>
       </c>
       <c r="J370" s="5" t="n">
-        <v>-1.669</v>
+        <v>0.658</v>
       </c>
       <c r="K370" s="5" t="n">
-        <v>-2.375</v>
+        <v>2.259</v>
       </c>
       <c r="L370" s="5" t="n">
-        <v>-2.744</v>
+        <v>5.141</v>
       </c>
       <c r="M370" t="inlineStr">
         <is>
@@ -27287,10 +27327,14 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Other income -government assistance (note 16)</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr"/>
+          <t>Selling, general and administrative expenses (note 15)</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
@@ -27306,15 +27350,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H371" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I371" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H371" s="5" t="n">
+        <v>2.067</v>
+      </c>
+      <c r="I371" s="5" t="n">
+        <v>3.299</v>
       </c>
       <c r="J371" t="inlineStr">
         <is>
@@ -27322,10 +27362,10 @@
         </is>
       </c>
       <c r="K371" s="5" t="n">
-        <v>0.207</v>
+        <v>2.918</v>
       </c>
       <c r="L371" s="5" t="n">
-        <v>0.84</v>
+        <v>3.134</v>
       </c>
       <c r="M371" t="inlineStr">
         <is>
@@ -27346,12 +27386,12 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Income (loss) before income taxes</t>
+          <t>Income (loss) from operations</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -27385,10 +27425,10 @@
         </is>
       </c>
       <c r="K372" s="5" t="n">
-        <v>-2.827</v>
+        <v>-0.659</v>
       </c>
       <c r="L372" s="5" t="n">
-        <v>0.103</v>
+        <v>2.007</v>
       </c>
       <c r="M372" t="inlineStr">
         <is>
@@ -27409,12 +27449,12 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Income tax (expense) recovery (note 10)</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -27433,21 +27473,19 @@
         </is>
       </c>
       <c r="H373" s="5" t="n">
-        <v>-0.839</v>
+        <v>-0.898</v>
       </c>
       <c r="I373" s="5" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="J373" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.16</v>
+      </c>
+      <c r="J373" s="5" t="n">
+        <v>-1.669</v>
       </c>
       <c r="K373" s="5" t="n">
-        <v>0.774</v>
+        <v>-2.375</v>
       </c>
       <c r="L373" s="5" t="n">
-        <v>-0.048</v>
+        <v>-2.744</v>
       </c>
       <c r="M373" t="inlineStr">
         <is>
@@ -27468,14 +27506,10 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Net income (loss) and comprehensive income (loss) for the year</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Other income -government assistance (note 16)</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
@@ -27507,10 +27541,10 @@
         </is>
       </c>
       <c r="K374" s="5" t="n">
-        <v>-2.053</v>
+        <v>0.207</v>
       </c>
       <c r="L374" s="5" t="n">
-        <v>0.055</v>
+        <v>0.84</v>
       </c>
       <c r="M374" t="inlineStr">
         <is>
@@ -27531,12 +27565,12 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Basic and diluted income (loss) per share $</t>
+          <t>Income (loss) before income taxes</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -27570,10 +27604,10 @@
         </is>
       </c>
       <c r="K375" s="5" t="n">
-        <v>-4e-08</v>
+        <v>-2.827</v>
       </c>
       <c r="L375" s="5" t="n">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="M375" t="inlineStr">
         <is>
@@ -27589,17 +27623,17 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>ended           ended</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Income tax (expense) recovery (note 10)</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -27618,19 +27652,21 @@
         </is>
       </c>
       <c r="H376" s="5" t="n">
-        <v>54.727382</v>
+        <v>-0.839</v>
       </c>
       <c r="I376" s="5" t="n">
-        <v>45.056648</v>
-      </c>
-      <c r="J376" s="5" t="n">
-        <v>45.718565</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K376" s="5" t="n">
-        <v>46.425824</v>
+        <v>0.774</v>
       </c>
       <c r="L376" s="5" t="n">
-        <v>46.963929</v>
+        <v>-0.048</v>
       </c>
       <c r="M376" t="inlineStr">
         <is>
@@ -27646,17 +27682,17 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>ended           ended</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Diluted</t>
+          <t>Net income (loss) and comprehensive income (loss) for the year</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>DilutedAverageShares</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -27674,20 +27710,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H377" s="5" t="n">
-        <v>56.393848</v>
-      </c>
-      <c r="I377" s="5" t="n">
-        <v>45.056648</v>
-      </c>
-      <c r="J377" s="5" t="n">
-        <v>45.718565</v>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K377" s="5" t="n">
-        <v>46.425824</v>
+        <v>-2.053</v>
       </c>
       <c r="L377" s="5" t="n">
-        <v>47.126244</v>
+        <v>0.055</v>
       </c>
       <c r="M377" t="inlineStr">
         <is>
@@ -27703,15 +27745,19 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Bearer pants</t>
+          <t>ended           ended</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>($000s) December 31, 2024 December</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr"/>
+          <t>Basic and diluted income (loss) per share $</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -27743,10 +27789,10 @@
         </is>
       </c>
       <c r="K378" s="5" t="n">
-        <v>2.023</v>
+        <v>-4e-08</v>
       </c>
       <c r="L378" s="5" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="M378" t="inlineStr">
         <is>
@@ -27762,15 +27808,19 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Bearer pants</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Bearer plants – beginning of the year</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr"/>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
@@ -27786,26 +27836,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H379" s="5" t="n">
+        <v>54.727382</v>
+      </c>
+      <c r="I379" s="5" t="n">
+        <v>45.056648</v>
+      </c>
+      <c r="J379" s="5" t="n">
+        <v>45.718565</v>
       </c>
       <c r="K379" s="5" t="n">
-        <v>1.691</v>
+        <v>46.425824</v>
       </c>
       <c r="L379" s="5" t="n">
-        <v>1.731</v>
+        <v>46.963929</v>
       </c>
       <c r="M379" t="inlineStr">
         <is>
@@ -27821,15 +27865,19 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Bearer pants</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Additions reclassified from inventory</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr"/>
+          <t>Diluted</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
@@ -27845,26 +27893,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H380" s="5" t="n">
+        <v>56.393848</v>
+      </c>
+      <c r="I380" s="5" t="n">
+        <v>45.056648</v>
+      </c>
+      <c r="J380" s="5" t="n">
+        <v>45.718565</v>
       </c>
       <c r="K380" s="5" t="n">
-        <v>0.157</v>
+        <v>46.425824</v>
       </c>
       <c r="L380" s="5" t="n">
-        <v>0.743</v>
+        <v>47.126244</v>
       </c>
       <c r="M380" t="inlineStr">
         <is>
@@ -27885,7 +27927,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Additions acquired</t>
+          <t>($000s) December 31, 2024 December</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -27920,10 +27962,10 @@
         </is>
       </c>
       <c r="K381" s="5" t="n">
-        <v>5.494</v>
+        <v>2.023</v>
       </c>
       <c r="L381" s="5" t="n">
-        <v>4.9</v>
+        <v>0.031</v>
       </c>
       <c r="M381" t="inlineStr">
         <is>
@@ -27944,7 +27986,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Depreciation of bearer plants</t>
+          <t>Bearer plants – beginning of the year</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -27979,10 +28021,10 @@
         </is>
       </c>
       <c r="K382" s="5" t="n">
-        <v>-5.611</v>
+        <v>1.691</v>
       </c>
       <c r="L382" s="5" t="n">
-        <v>-5.379</v>
+        <v>1.731</v>
       </c>
       <c r="M382" t="inlineStr">
         <is>
@@ -28003,7 +28045,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Bearer plants – end of the year</t>
+          <t>Additions reclassified from inventory</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -28038,10 +28080,10 @@
         </is>
       </c>
       <c r="K383" s="5" t="n">
-        <v>1.731</v>
+        <v>0.157</v>
       </c>
       <c r="L383" s="5" t="n">
-        <v>1.995</v>
+        <v>0.743</v>
       </c>
       <c r="M383" t="inlineStr">
         <is>
@@ -28057,12 +28099,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>for tomatoes and five weeks for mini peppers.</t>
+          <t>Bearer pants</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>($000s) December 31, 2024 December</t>
+          <t>Additions acquired</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -28097,10 +28139,10 @@
         </is>
       </c>
       <c r="K384" s="5" t="n">
-        <v>2.023</v>
+        <v>5.494</v>
       </c>
       <c r="L384" s="5" t="n">
-        <v>0.031</v>
+        <v>4.9</v>
       </c>
       <c r="M384" t="inlineStr">
         <is>
@@ -28116,12 +28158,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>for tomatoes and five weeks for mini peppers.</t>
+          <t>Bearer pants</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Biological assets – beginning of the year</t>
+          <t>Depreciation of bearer plants</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -28155,15 +28197,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K385" s="5" t="n">
+        <v>-5.611</v>
+      </c>
+      <c r="L385" s="5" t="n">
+        <v>-5.379</v>
       </c>
       <c r="M385" t="inlineStr">
         <is>
@@ -28179,12 +28217,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>for tomatoes and five weeks for mini peppers.</t>
+          <t>Bearer pants</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Unrealized gains due to biological asset transformation</t>
+          <t>Bearer plants – end of the year</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -28219,10 +28257,10 @@
         </is>
       </c>
       <c r="K386" s="5" t="n">
-        <v>22.015</v>
+        <v>1.731</v>
       </c>
       <c r="L386" s="5" t="n">
-        <v>25.422</v>
+        <v>1.995</v>
       </c>
       <c r="M386" t="inlineStr">
         <is>
@@ -28243,7 +28281,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Fair value of harvested biological asset</t>
+          <t>($000s) December 31, 2024 December</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -28278,10 +28316,10 @@
         </is>
       </c>
       <c r="K387" s="5" t="n">
-        <v>-22.015</v>
+        <v>2.023</v>
       </c>
       <c r="L387" s="5" t="n">
-        <v>-25.422</v>
+        <v>0.031</v>
       </c>
       <c r="M387" t="inlineStr">
         <is>
@@ -28302,7 +28340,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Biological assets – end of the year</t>
+          <t>Biological assets – beginning of the year</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -28360,12 +28398,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>for tomatoes and five weeks for mini peppers.</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Balance – December 31, 2023 6,470 44,338 2,833 7,444 45</t>
+          <t>Unrealized gains due to biological asset transformation</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -28400,10 +28438,10 @@
         </is>
       </c>
       <c r="K389" s="5" t="n">
-        <v>61.843</v>
+        <v>22.015</v>
       </c>
       <c r="L389" s="5" t="n">
-        <v>0.713</v>
+        <v>25.422</v>
       </c>
       <c r="M389" t="inlineStr">
         <is>
@@ -28419,12 +28457,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>for tomatoes and five weeks for mini peppers.</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Additions - 40 66 69 -</t>
+          <t>Fair value of harvested biological asset</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -28459,12 +28497,10 @@
         </is>
       </c>
       <c r="K390" s="5" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="L390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-22.015</v>
+      </c>
+      <c r="L390" s="5" t="n">
+        <v>-25.422</v>
       </c>
       <c r="M390" t="inlineStr">
         <is>
@@ -28480,12 +28516,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>for tomatoes and five weeks for mini peppers.</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Balance – December 31, 2024 6,470 44,378 2,899 7,513 45</t>
+          <t>Biological assets – end of the year</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -28519,11 +28555,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K391" s="5" t="n">
-        <v>62.018</v>
-      </c>
-      <c r="L391" s="5" t="n">
-        <v>0.713</v>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M391" t="inlineStr">
         <is>
@@ -28539,12 +28579,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Accumulated depreciation</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Balance – December 31, 2023 - 7,735 360 2,637 12</t>
+          <t>Balance – December 31, 2023 6,470 44,338 2,833 7,444 45</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
@@ -28579,10 +28619,10 @@
         </is>
       </c>
       <c r="K392" s="5" t="n">
-        <v>11.274</v>
+        <v>61.843</v>
       </c>
       <c r="L392" s="5" t="n">
-        <v>0.53</v>
+        <v>0.713</v>
       </c>
       <c r="M392" t="inlineStr">
         <is>
@@ -28598,12 +28638,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Accumulated depreciation</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Additions - 1,796 115 753 5</t>
+          <t>Additions - 40 66 69 -</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
@@ -28638,10 +28678,12 @@
         </is>
       </c>
       <c r="K393" s="5" t="n">
-        <v>2.801</v>
-      </c>
-      <c r="L393" s="5" t="n">
-        <v>0.132</v>
+        <v>0.175</v>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M393" t="inlineStr">
         <is>
@@ -28657,12 +28699,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Accumulated depreciation</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Balance – December, 2024 - 9,531 475 3,390 17</t>
+          <t>Balance – December 31, 2024 6,470 44,378 2,899 7,513 45</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
@@ -28697,10 +28739,10 @@
         </is>
       </c>
       <c r="K394" s="5" t="n">
-        <v>14.075</v>
+        <v>62.018</v>
       </c>
       <c r="L394" s="5" t="n">
-        <v>0.662</v>
+        <v>0.713</v>
       </c>
       <c r="M394" t="inlineStr">
         <is>
@@ -28716,12 +28758,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Net book value</t>
+          <t>Accumulated depreciation</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Balance – December 31, 2024 6,470 34,847 2,424 4,123 28</t>
+          <t>Balance – December 31, 2023 - 7,735 360 2,637 12</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -28756,10 +28798,10 @@
         </is>
       </c>
       <c r="K395" s="5" t="n">
-        <v>47.943</v>
+        <v>11.274</v>
       </c>
       <c r="L395" s="5" t="n">
-        <v>0.051</v>
+        <v>0.53</v>
       </c>
       <c r="M395" t="inlineStr">
         <is>
@@ -28775,12 +28817,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>Accumulated depreciation</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Balance – December 31, 2022 6,470 44,332 2,806 6,950 45</t>
+          <t>Additions - 1,796 115 753 5</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -28815,10 +28857,10 @@
         </is>
       </c>
       <c r="K396" s="5" t="n">
-        <v>61.211</v>
+        <v>2.801</v>
       </c>
       <c r="L396" s="5" t="n">
-        <v>0.608</v>
+        <v>0.132</v>
       </c>
       <c r="M396" t="inlineStr">
         <is>
@@ -28834,12 +28876,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>Accumulated depreciation</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Additions - 6 27 494 -</t>
+          <t>Balance – December, 2024 - 9,531 475 3,390 17</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
@@ -28874,10 +28916,10 @@
         </is>
       </c>
       <c r="K397" s="5" t="n">
-        <v>0.632</v>
+        <v>14.075</v>
       </c>
       <c r="L397" s="5" t="n">
-        <v>0.105</v>
+        <v>0.662</v>
       </c>
       <c r="M397" t="inlineStr">
         <is>
@@ -28893,12 +28935,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Accumulated depreciation</t>
+          <t>Net book value</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Balance – December 31, 2022 - 5,835 247 1,926 7</t>
+          <t>Balance – December 31, 2024 6,470 34,847 2,424 4,123 28</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
@@ -28933,10 +28975,10 @@
         </is>
       </c>
       <c r="K398" s="5" t="n">
-        <v>8.393000000000001</v>
+        <v>47.943</v>
       </c>
       <c r="L398" s="5" t="n">
-        <v>0.378</v>
+        <v>0.051</v>
       </c>
       <c r="M398" t="inlineStr">
         <is>
@@ -28952,12 +28994,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Accumulated depreciation</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Additions - 1,900 113 711 5</t>
+          <t>Balance – December 31, 2022 6,470 44,332 2,806 6,950 45</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -28992,10 +29034,10 @@
         </is>
       </c>
       <c r="K399" s="5" t="n">
-        <v>2.881</v>
+        <v>61.211</v>
       </c>
       <c r="L399" s="5" t="n">
-        <v>0.152</v>
+        <v>0.608</v>
       </c>
       <c r="M399" t="inlineStr">
         <is>
@@ -29011,12 +29053,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Accumulated depreciation</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Balance – December, 2023 - 7,735 360 2,637 12</t>
+          <t>Additions - 6 27 494 -</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -29051,10 +29093,10 @@
         </is>
       </c>
       <c r="K400" s="5" t="n">
-        <v>11.274</v>
+        <v>0.632</v>
       </c>
       <c r="L400" s="5" t="n">
-        <v>0.53</v>
+        <v>0.105</v>
       </c>
       <c r="M400" t="inlineStr">
         <is>
@@ -29070,12 +29112,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Net book value</t>
+          <t>Accumulated depreciation</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Balance – December 31, 2023 6,470 36,603 2,473 4,807 33</t>
+          <t>Balance – December 31, 2022 - 5,835 247 1,926 7</t>
         </is>
       </c>
       <c r="D401" t="inlineStr"/>
@@ -29110,10 +29152,10 @@
         </is>
       </c>
       <c r="K401" s="5" t="n">
-        <v>50.569</v>
+        <v>8.393000000000001</v>
       </c>
       <c r="L401" s="5" t="n">
-        <v>0.183</v>
+        <v>0.378</v>
       </c>
       <c r="M401" t="inlineStr">
         <is>
@@ -29129,12 +29171,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Continuity schedule</t>
+          <t>Accumulated depreciation</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>($000s) December 31, 2024 December</t>
+          <t>Additions - 1,900 113 711 5</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
@@ -29169,10 +29211,10 @@
         </is>
       </c>
       <c r="K402" s="5" t="n">
-        <v>2.023</v>
+        <v>2.881</v>
       </c>
       <c r="L402" s="5" t="n">
-        <v>0.031</v>
+        <v>0.152</v>
       </c>
       <c r="M402" t="inlineStr">
         <is>
@@ -29188,12 +29230,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Continuity schedule</t>
+          <t>Accumulated depreciation</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Lease obligations – beginning of the year</t>
+          <t>Balance – December, 2023 - 7,735 360 2,637 12</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -29228,10 +29270,10 @@
         </is>
       </c>
       <c r="K403" s="5" t="n">
-        <v>0.297</v>
+        <v>11.274</v>
       </c>
       <c r="L403" s="5" t="n">
-        <v>0.251</v>
+        <v>0.53</v>
       </c>
       <c r="M403" t="inlineStr">
         <is>
@@ -29247,12 +29289,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Continuity schedule</t>
+          <t>Net book value</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Additions during the year</t>
+          <t>Balance – December 31, 2023 6,470 36,603 2,473 4,807 33</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -29287,12 +29329,10 @@
         </is>
       </c>
       <c r="K404" s="5" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="L404" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>50.569</v>
+      </c>
+      <c r="L404" s="5" t="n">
+        <v>0.183</v>
       </c>
       <c r="M404" t="inlineStr">
         <is>
@@ -29313,7 +29353,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Lease payments, excluding interest</t>
+          <t>($000s) December 31, 2024 December</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
@@ -29348,10 +29388,10 @@
         </is>
       </c>
       <c r="K405" s="5" t="n">
-        <v>-0.151</v>
+        <v>2.023</v>
       </c>
       <c r="L405" s="5" t="n">
-        <v>-0.162</v>
+        <v>0.031</v>
       </c>
       <c r="M405" t="inlineStr">
         <is>
@@ -29372,7 +29412,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Less: Current portion</t>
+          <t>Lease obligations – beginning of the year</t>
         </is>
       </c>
       <c r="D406" t="inlineStr"/>
@@ -29407,10 +29447,10 @@
         </is>
       </c>
       <c r="K406" s="5" t="n">
-        <v>-0.133</v>
+        <v>0.297</v>
       </c>
       <c r="L406" s="5" t="n">
-        <v>-0.081</v>
+        <v>0.251</v>
       </c>
       <c r="M406" t="inlineStr">
         <is>
@@ -29431,7 +29471,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Long term lease obligations – end of the year</t>
+          <t>Additions during the year</t>
         </is>
       </c>
       <c r="D407" t="inlineStr"/>
@@ -29466,10 +29506,12 @@
         </is>
       </c>
       <c r="K407" s="5" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="L407" s="5" t="n">
-        <v>0.008</v>
+        <v>0.105</v>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M407" t="inlineStr">
         <is>
@@ -29490,7 +29532,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Current lease obligations -end of year</t>
+          <t>Lease payments, excluding interest</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
@@ -29525,10 +29567,10 @@
         </is>
       </c>
       <c r="K408" s="5" t="n">
-        <v>0.133</v>
+        <v>-0.151</v>
       </c>
       <c r="L408" s="5" t="n">
-        <v>0.081</v>
+        <v>-0.162</v>
       </c>
       <c r="M408" t="inlineStr">
         <is>
@@ -29549,7 +29591,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Long term lease obligations -end of year</t>
+          <t>Less: Current portion</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
@@ -29584,10 +29626,10 @@
         </is>
       </c>
       <c r="K409" s="5" t="n">
-        <v>0.118</v>
+        <v>-0.133</v>
       </c>
       <c r="L409" s="5" t="n">
-        <v>0.008</v>
+        <v>-0.081</v>
       </c>
       <c r="M409" t="inlineStr">
         <is>
@@ -29608,7 +29650,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Total lease obligations – end of the year</t>
+          <t>Long term lease obligations – end of the year</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
@@ -29643,10 +29685,10 @@
         </is>
       </c>
       <c r="K410" s="5" t="n">
-        <v>0.251</v>
+        <v>0.118</v>
       </c>
       <c r="L410" s="5" t="n">
-        <v>0.089</v>
+        <v>0.008</v>
       </c>
       <c r="M410" t="inlineStr">
         <is>
@@ -29662,19 +29704,15 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>ended           ended</t>
+          <t>Continuity schedule</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Revenue (note 13) $</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Current lease obligations -end of year</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -29695,19 +29733,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I411" s="5" t="n">
-        <v>17.711</v>
-      </c>
-      <c r="J411" s="5" t="n">
-        <v>23.056</v>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K411" s="5" t="n">
-        <v>26.47</v>
-      </c>
-      <c r="L411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.133</v>
+      </c>
+      <c r="L411" s="5" t="n">
+        <v>0.081</v>
       </c>
       <c r="M411" t="inlineStr">
         <is>
@@ -29723,19 +29763,15 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>ended           ended</t>
+          <t>Continuity schedule</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Cost of sales (note 14)</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
+          <t>Long term lease obligations -end of year</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
@@ -29756,19 +29792,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I412" s="5" t="n">
-        <v>17.477</v>
-      </c>
-      <c r="J412" s="5" t="n">
-        <v>22.398</v>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K412" s="5" t="n">
-        <v>24.211</v>
-      </c>
-      <c r="L412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.118</v>
+      </c>
+      <c r="L412" s="5" t="n">
+        <v>0.008</v>
       </c>
       <c r="M412" t="inlineStr">
         <is>
@@ -29784,19 +29822,15 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>ended           ended</t>
+          <t>Continuity schedule</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses (note 14)</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Total lease obligations – end of the year</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr">
         <is>
           <t>-</t>
@@ -29817,19 +29851,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I413" s="5" t="n">
-        <v>3.299</v>
-      </c>
-      <c r="J413" s="5" t="n">
-        <v>3.209</v>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K413" s="5" t="n">
-        <v>2.918</v>
-      </c>
-      <c r="L413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.251</v>
+      </c>
+      <c r="L413" s="5" t="n">
+        <v>0.089</v>
       </c>
       <c r="M413" t="inlineStr">
         <is>
@@ -29850,12 +29886,12 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Loss from operations</t>
+          <t>Revenue (note 13) $</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -29879,13 +29915,13 @@
         </is>
       </c>
       <c r="I414" s="5" t="n">
-        <v>-3.065</v>
+        <v>17.711</v>
       </c>
       <c r="J414" s="5" t="n">
-        <v>-2.551</v>
+        <v>23.056</v>
       </c>
       <c r="K414" s="5" t="n">
-        <v>-0.659</v>
+        <v>26.47</v>
       </c>
       <c r="L414" t="inlineStr">
         <is>
@@ -29911,10 +29947,14 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Other income -government assistance (note 15)</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr"/>
+          <t>Cost of sales (note 14)</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
           <t>-</t>
@@ -29935,16 +29975,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I415" s="5" t="n">
+        <v>17.477</v>
       </c>
       <c r="J415" s="5" t="n">
-        <v>2.281</v>
+        <v>22.398</v>
       </c>
       <c r="K415" s="5" t="n">
-        <v>0.207</v>
+        <v>24.211</v>
       </c>
       <c r="L415" t="inlineStr">
         <is>
@@ -29970,12 +30008,12 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
+          <t>Selling, general and administrative expenses (note 14)</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -29999,13 +30037,13 @@
         </is>
       </c>
       <c r="I416" s="5" t="n">
-        <v>-4.225</v>
+        <v>3.299</v>
       </c>
       <c r="J416" s="5" t="n">
-        <v>-1.939</v>
+        <v>3.209</v>
       </c>
       <c r="K416" s="5" t="n">
-        <v>-2.827</v>
+        <v>2.918</v>
       </c>
       <c r="L416" t="inlineStr">
         <is>
@@ -30031,10 +30069,14 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Income tax recovery (note 9)</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr"/>
+          <t>Loss from operations</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -30056,13 +30098,13 @@
         </is>
       </c>
       <c r="I417" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>-3.065</v>
       </c>
       <c r="J417" s="5" t="n">
-        <v>0.171</v>
+        <v>-2.551</v>
       </c>
       <c r="K417" s="5" t="n">
-        <v>0.774</v>
+        <v>-0.659</v>
       </c>
       <c r="L417" t="inlineStr">
         <is>
@@ -30088,14 +30130,10 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Other income -government assistance (note 15)</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
@@ -30116,14 +30154,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I418" s="5" t="n">
-        <v>-3.415</v>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J418" s="5" t="n">
-        <v>-1.768</v>
+        <v>2.281</v>
       </c>
       <c r="K418" s="5" t="n">
-        <v>-2.053</v>
+        <v>0.207</v>
       </c>
       <c r="L418" t="inlineStr">
         <is>
@@ -30149,12 +30189,12 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
+          <t>Loss before income taxes</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -30178,13 +30218,13 @@
         </is>
       </c>
       <c r="I419" s="5" t="n">
-        <v>-8e-08</v>
+        <v>-4.225</v>
       </c>
       <c r="J419" s="5" t="n">
-        <v>-4e-08</v>
+        <v>-1.939</v>
       </c>
       <c r="K419" s="5" t="n">
-        <v>-4e-08</v>
+        <v>-2.827</v>
       </c>
       <c r="L419" t="inlineStr">
         <is>
@@ -30203,13 +30243,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B420" t="inlineStr"/>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>ended           ended</t>
+        </is>
+      </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>For the years ended December 31, 2022 and December</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr"/>
+          <t>Income tax recovery (note 9)</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -30231,15 +30279,13 @@
         </is>
       </c>
       <c r="I420" s="5" t="n">
-        <v>2.021</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J420" s="5" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="K420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.171</v>
+      </c>
+      <c r="K420" s="5" t="n">
+        <v>0.774</v>
       </c>
       <c r="L420" t="inlineStr">
         <is>
@@ -30265,10 +30311,14 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>(thousands, except number of shares and per share amounts) 31, 2022</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E421" t="inlineStr">
         <is>
           <t>-</t>
@@ -30290,15 +30340,13 @@
         </is>
       </c>
       <c r="I421" s="5" t="n">
-        <v>0.002021</v>
+        <v>-3.415</v>
       </c>
       <c r="J421" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="K421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.768</v>
+      </c>
+      <c r="K421" s="5" t="n">
+        <v>-2.053</v>
       </c>
       <c r="L421" t="inlineStr">
         <is>
@@ -30317,13 +30365,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B422" t="inlineStr"/>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>ended           ended</t>
+        </is>
+      </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>For the years ended December 31, 2021 and December</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr"/>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
           <t>-</t>
@@ -30339,21 +30395,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H422" s="5" t="n">
-        <v>2.02</v>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I422" s="5" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="J422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8e-08</v>
+      </c>
+      <c r="J422" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="K422" s="5" t="n">
+        <v>-4e-08</v>
       </c>
       <c r="L422" t="inlineStr">
         <is>
@@ -30372,14 +30426,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>ended           ended</t>
-        </is>
-      </c>
+      <c r="B423" t="inlineStr"/>
       <c r="C423" t="inlineStr">
         <is>
-          <t>(thousands, except per share amounts) 31, 2021</t>
+          <t>For the years ended December 31, 2022 and December</t>
         </is>
       </c>
       <c r="D423" t="inlineStr"/>
@@ -30398,16 +30448,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H423" s="5" t="n">
-        <v>0.00202</v>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I423" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="J423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.021</v>
+      </c>
+      <c r="J423" s="5" t="n">
+        <v>0.031</v>
       </c>
       <c r="K423" t="inlineStr">
         <is>
@@ -30438,14 +30488,10 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Earnings (loss) from operations</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>(thousands, except number of shares and per share amounts) 31, 2022</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
       <c r="E424" t="inlineStr">
         <is>
           <t>-</t>
@@ -30461,16 +30507,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H424" s="5" t="n">
-        <v>2.602</v>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I424" s="5" t="n">
-        <v>-3.065</v>
-      </c>
-      <c r="J424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002021</v>
+      </c>
+      <c r="J424" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="K424" t="inlineStr">
         <is>
@@ -30494,21 +30540,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>ended           ended</t>
-        </is>
-      </c>
+      <c r="B425" t="inlineStr"/>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Earnings (loss) before income taxes</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>For the years ended December 31, 2021 and December</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>
@@ -30525,10 +30563,10 @@
         </is>
       </c>
       <c r="H425" s="5" t="n">
-        <v>1.704</v>
+        <v>2.02</v>
       </c>
       <c r="I425" s="5" t="n">
-        <v>-4.225</v>
+        <v>0.031</v>
       </c>
       <c r="J425" t="inlineStr">
         <is>
@@ -30564,14 +30602,10 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Net earnings (loss) and comprehensive earnings (loss) for the year</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>(thousands, except per share amounts) 31, 2021</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr">
         <is>
           <t>-</t>
@@ -30588,10 +30622,10 @@
         </is>
       </c>
       <c r="H426" s="5" t="n">
-        <v>0.865</v>
+        <v>0.00202</v>
       </c>
       <c r="I426" s="5" t="n">
-        <v>-3.415</v>
+        <v>3.1e-05</v>
       </c>
       <c r="J426" t="inlineStr">
         <is>
@@ -30627,10 +30661,14 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Basic and diluted earnings (loss) per share $</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr"/>
+          <t>Earnings (loss) from operations</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -30647,10 +30685,10 @@
         </is>
       </c>
       <c r="H427" s="5" t="n">
-        <v>2e-08</v>
+        <v>2.602</v>
       </c>
       <c r="I427" s="5" t="n">
-        <v>-8e-08</v>
+        <v>-3.065</v>
       </c>
       <c r="J427" t="inlineStr">
         <is>
@@ -30681,35 +30719,39 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>ended   March 21, 2018 (date of</t>
+          <t>ended           ended</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>(thousands, except share and per share amounts) 2019 December</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr"/>
+          <t>Earnings (loss) before income taxes</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F428" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="G428" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="H428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H428" s="5" t="n">
+        <v>1.704</v>
+      </c>
+      <c r="I428" s="5" t="n">
+        <v>-4.225</v>
       </c>
       <c r="J428" t="inlineStr">
         <is>
@@ -30740,17 +30782,17 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>ended   March 21, 2018 (date of</t>
+          <t>ended           ended</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Revenue (note 13) $</t>
+          <t>Net earnings (loss) and comprehensive earnings (loss) for the year</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -30758,21 +30800,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F429" s="5" t="n">
-        <v>8.324</v>
-      </c>
-      <c r="G429" s="5" t="n">
-        <v>13.697</v>
-      </c>
-      <c r="H429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H429" s="5" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="I429" s="5" t="n">
+        <v>-3.415</v>
       </c>
       <c r="J429" t="inlineStr">
         <is>
@@ -30803,39 +30845,35 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>ended   March 21, 2018 (date of</t>
+          <t>ended           ended</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Cost of sales (note 14)</t>
-        </is>
-      </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
+          <t>Basic and diluted earnings (loss) per share $</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F430" s="5" t="n">
-        <v>7.142</v>
-      </c>
-      <c r="G430" s="5" t="n">
-        <v>11.062</v>
-      </c>
-      <c r="H430" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I430" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H430" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="I430" s="5" t="n">
+        <v>-8e-08</v>
       </c>
       <c r="J430" t="inlineStr">
         <is>
@@ -30871,24 +30909,20 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
+          <t>(thousands, except share and per share amounts) 2019 December</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F431" s="5" t="n">
-        <v>1.182</v>
+        <v>0.002018</v>
       </c>
       <c r="G431" s="5" t="n">
-        <v>2.635</v>
+        <v>3.1e-05</v>
       </c>
       <c r="H431" t="inlineStr">
         <is>
@@ -30934,12 +30968,12 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses (note 14)</t>
+          <t>Revenue (note 13) $</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -30948,10 +30982,10 @@
         </is>
       </c>
       <c r="F432" s="5" t="n">
-        <v>0.746</v>
+        <v>8.324</v>
       </c>
       <c r="G432" s="5" t="n">
-        <v>1.735</v>
+        <v>13.697</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
@@ -30997,20 +31031,24 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Earnings from operations</t>
-        </is>
-      </c>
-      <c r="D433" t="inlineStr"/>
+          <t>Cost of sales (note 14)</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F433" s="5" t="n">
-        <v>0.436</v>
+        <v>7.142</v>
       </c>
       <c r="G433" s="5" t="n">
-        <v>0.9</v>
+        <v>11.062</v>
       </c>
       <c r="H433" t="inlineStr">
         <is>
@@ -31056,12 +31094,12 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Interest expense</t>
+          <t>Gross profit</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>GrossProfit</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -31070,10 +31108,10 @@
         </is>
       </c>
       <c r="F434" s="5" t="n">
-        <v>-0.5659999999999999</v>
+        <v>1.182</v>
       </c>
       <c r="G434" s="5" t="n">
-        <v>-0.999</v>
+        <v>2.635</v>
       </c>
       <c r="H434" t="inlineStr">
         <is>
@@ -31119,22 +31157,24 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Listing expense (note 4)</t>
-        </is>
-      </c>
-      <c r="D435" t="inlineStr"/>
+          <t>Selling, general and administrative expenses (note 14)</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F435" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F435" s="5" t="n">
+        <v>0.746</v>
       </c>
       <c r="G435" s="5" t="n">
-        <v>-2.317</v>
+        <v>1.735</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
@@ -31180,22 +31220,24 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Bargain purchase gain (note 5)</t>
-        </is>
-      </c>
-      <c r="D436" t="inlineStr"/>
+          <t>Earnings from operations</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F436" s="5" t="n">
-        <v>3.752</v>
-      </c>
-      <c r="G436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.436</v>
+      </c>
+      <c r="G436" s="5" t="n">
+        <v>0.9</v>
       </c>
       <c r="H436" t="inlineStr">
         <is>
@@ -31241,12 +31283,12 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Earnings (loss) before income taxes</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -31255,10 +31297,10 @@
         </is>
       </c>
       <c r="F437" s="5" t="n">
-        <v>3.622</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="G437" s="5" t="n">
-        <v>-2.416</v>
+        <v>-0.999</v>
       </c>
       <c r="H437" t="inlineStr">
         <is>
@@ -31304,24 +31346,22 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Deferred income tax (expense) recovery</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Listing expense (note 4)</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr"/>
       <c r="E438" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F438" s="5" t="n">
-        <v>0.033</v>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G438" s="5" t="n">
-        <v>0.181</v>
+        <v>-2.317</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>
@@ -31367,24 +31407,22 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Net earnings (loss) and comprehensive earnings (loss) for the period</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Bargain purchase gain (note 5)</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr"/>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F439" s="5" t="n">
-        <v>3.655</v>
-      </c>
-      <c r="G439" s="5" t="n">
-        <v>-2.235</v>
+        <v>3.752</v>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H439" t="inlineStr">
         <is>
@@ -31430,20 +31468,24 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Basic and diluted earnings (loss) per share $</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr"/>
+          <t>Earnings (loss) before income taxes</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E440" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F440" s="5" t="n">
-        <v>1.2e-07</v>
+        <v>3.622</v>
       </c>
       <c r="G440" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>-2.416</v>
       </c>
       <c r="H440" t="inlineStr">
         <is>
@@ -31489,12 +31531,12 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Deferred income tax (expense) recovery</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -31503,10 +31545,10 @@
         </is>
       </c>
       <c r="F441" s="5" t="n">
-        <v>30</v>
+        <v>0.033</v>
       </c>
       <c r="G441" s="5" t="n">
-        <v>37.527813</v>
+        <v>0.181</v>
       </c>
       <c r="H441" t="inlineStr">
         <is>
@@ -31547,52 +31589,237 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
+          <t>ended   March 21, 2018 (date of</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Net earnings (loss) and comprehensive earnings (loss) for the period</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F442" s="5" t="n">
+        <v>3.655</v>
+      </c>
+      <c r="G442" s="5" t="n">
+        <v>-2.235</v>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>ended   March 21, 2018 (date of</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Basic and diluted earnings (loss) per share $</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr"/>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F443" s="5" t="n">
+        <v>1.2e-07</v>
+      </c>
+      <c r="G443" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>ended   March 21, 2018 (date of</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F444" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G444" s="5" t="n">
+        <v>37.527813</v>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
           <t>Buildings     Greenhouses      equipment</t>
         </is>
       </c>
-      <c r="C442" t="inlineStr">
+      <c r="C445" t="inlineStr">
         <is>
           <t>Years 25 5 -</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
-      <c r="E442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F442" s="5" t="n">
+      <c r="D445" t="inlineStr"/>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F445" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="G442" s="5" t="n">
+      <c r="G445" s="5" t="n">
         <v>0.025</v>
       </c>
-      <c r="H442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M442" t="inlineStr">
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
         <is>
           <t>-</t>
         </is>
